--- a/Grading Scheme/CS4800 Grading Scheme.xlsx
+++ b/Grading Scheme/CS4800 Grading Scheme.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365.sharepoint.com/sites/stud-CS4800-SustainableICT/Gedeelde documenten/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4103304-9664-482F-8DED-2C8D36A8C805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C8BED7-D679-487C-B4A9-A126B85DA036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{1172C34F-1F46-43B9-92EF-666DBCB28265}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{1172C34F-1F46-43B9-92EF-666DBCB28265}"/>
   </bookViews>
   <sheets>
     <sheet name="AI" sheetId="1" r:id="rId1"/>
     <sheet name="Software" sheetId="2" r:id="rId2"/>
-    <sheet name="Presentation" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,30 +36,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>Section/Grade</t>
   </si>
@@ -293,127 +270,12 @@
     <t>• JIT performance impacts are presented and explained in a clear and complete way, e.g. with references from documentation
 • code changes related to JIT implementation that improve performance result from either abstract reasoning or deep understanding of the experiment or both, e.g. implementing changes that address stress hotspots</t>
   </si>
-  <si>
-    <t>Learning objective/Grade</t>
-  </si>
-  <si>
-    <t>Potential Questions</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LO3:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Students </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>apply techniques that minimize system climate impacts.</t>
-    </r>
-  </si>
-  <si>
-    <t>• impact of Part 1 design decisions on environment is not explained, or system is designed without taking into account environmental impacts</t>
-  </si>
-  <si>
-    <t>• connection between design decisions made in Part 1 and environmental impacts revealed in Part 2 explained in a vague or hard-to-follow manner, e.g. general statements that could apply to other systems</t>
-  </si>
-  <si>
-    <t>• connection between design decisions and environmental impacts explained in a clear way, with minor gaps in detail or organization</t>
-  </si>
-  <si>
-    <t>• connection between design decisions and environmental impacts explained in a clear and complete way, e.g. effect on sustainability flows down directly from system properties
-• system is designed in a manner that reduces environmental impact, or, if not, students can explain why this happens</t>
-  </si>
-  <si>
-    <t>• To what extent the implementation of JIT reduce/increase your code's energy consumption? Why?
-• Would selecting a different AI model architecture have decreased your system's environmental impact?
-• What does your experiment highlight about the sustainability of the real-life workload?</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LO4:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Students</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> analyze how each design technique affects system climate impacts.</t>
-    </r>
-  </si>
-  <si>
-    <t>• environmental impacts assessed in Part 2 are not presented</t>
-  </si>
-  <si>
-    <t>• results of environmental impact assessment presented in a vague or hard-to-follow manner, e.g. unclear whether emissions figures are CO2 or CO2-eq</t>
-  </si>
-  <si>
-    <t>• results of environmental impact assessment presented in a clear way, with minor gaps in detail or organization
-• recommendations for improvement given, with unclear applicability, e.g. change model architecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• aspects of the designed system that concentrate the most environmental impact are specially distinguished
-• clear, complete, and directly applicable recommendations for improvement given
-</t>
-  </si>
-  <si>
-    <t>• How much energy does your selected model architecture or training/inference method save compared to standard? Why?
-• Where are the energy hotspots in your workload? Do you think this also happens in real life? How would you address these hotspots?
-• Does your design minimize both the carbon footprint and the water footprint, or did you have to make a trade-off? Which did you pick and why?</t>
-  </si>
-  <si>
-    <t>Note: all criteria require a passing grade to obtain a passing grade for the assignment. All sub-criteria need to be met to obtain the maximum grade.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,14 +333,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -599,21 +453,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -697,10 +539,6 @@
     <xf numFmtId="10" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -708,7 +546,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="35"/>
     </xf>
@@ -1055,238 +892,238 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="44.42578125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="28"/>
-    <col min="8" max="8" width="44.42578125" style="28" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="28"/>
+    <col min="1" max="1" width="32.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="44.42578125" style="24" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="24"/>
+    <col min="8" max="8" width="44.42578125" style="24" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="30">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="26">
         <f>SUM(F3:F4)</f>
         <v>0.35</v>
       </c>
-      <c r="G2" s="31">
+      <c r="G2" s="27">
         <f>(F3*G3+F4*G4)/F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" ht="138" customHeight="1">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="29">
         <v>0.1</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="275.25" customHeight="1">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="29">
         <v>0.25</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="30">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="26">
         <f>SUM(F6:F8)</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="27">
         <f>(F6*G6+F7*G7+F8*G8)/F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="88.15" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="29">
         <v>0.05</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" ht="100.9">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="29">
         <v>0.45</v>
       </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="104.45" customHeight="1">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="29">
         <v>0.05</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="30">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="26">
         <f>SUM(F10)</f>
         <v>0.1</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="27">
         <f>F10*G10/F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="21"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" ht="76.150000000000006" customHeight="1">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="35">
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="31">
         <v>0.1</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="21"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="34">
         <f>SUM(F2, F5, F9)</f>
         <v>1</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="33">
         <f>F2*G2+F5*G5+F9*G9</f>
         <v>0</v>
       </c>
-      <c r="H11" s="21"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="13" spans="1:8" ht="15.6">
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="36" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1312,217 +1149,217 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="13">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="9">
         <f>SUM(F3:F4)</f>
         <v>0.5</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="10">
         <f>(F3*G3+F4*G4)/F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" ht="222" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="11">
         <v>0.35</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="21"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="207.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="11">
         <v>0.15</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="21"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="13">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="9">
         <f>SUM(F6:F8)</f>
         <v>0.39999999999999997</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="10">
         <f>(F6*G6+F7*G7+F8*G8)/F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="72">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="11">
         <v>0.05</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="21"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" ht="100.9">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="11">
         <v>0.3</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="21"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="100.9">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="11">
         <v>0.05</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="21"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="13">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="9">
         <f>SUM(F10)</f>
         <v>0.1</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="10">
         <f>F10*G10/F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="21"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" ht="72">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="17">
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="13">
         <v>0.1</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="21"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="15">
         <f>SUM(F2, F5, F9)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="16">
         <f>F2*G2+F5*G5+F9*G9</f>
         <v>0</v>
       </c>
-      <c r="H11" s="21"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="H12" s="21"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" ht="15.6">
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="36" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1534,127 +1371,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051E3901-2D00-4B7A-AF1E-750AA7A841D8}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
-  <cols>
-    <col min="1" max="5" width="27.7109375" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="65" customWidth="1"/>
-    <col min="9" max="9" width="41.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="158.44999999999999" customHeight="1">
-      <c r="A2" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="1:9" ht="117" customHeight="1">
-      <c r="A3" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="E4" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="38">
-        <f>SUM(F2:F3)</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="37" cm="1">
-        <f t="array" aca="1" ref="G4" ca="1">SUM(F2:F6*G2:G6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.6">
-      <c r="B6" s="42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006361CC30A796B45889DA9F9E9E6F319" ma:contentTypeVersion="4" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="33f50aab023f53500675ccc222439b76">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b500b7ef-b990-41a2-bdb4-ae3802c569fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a41cdd34851ef5004a4015d3774933e2" ns2:_="">
     <xsd:import namespace="b500b7ef-b990-41a2-bdb4-ae3802c569fe"/>
@@ -1798,23 +1530,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30D462F1-F2A3-4AE6-A472-4A62B656CC6F}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81DB541-4FCE-4FD3-94CA-D363D3702FA6}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51546482-E49B-48BF-8D1D-088803DCFEFD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30D462F1-F2A3-4AE6-A472-4A62B656CC6F}"/>
 </file>
--- a/Grading Scheme/CS4800 Grading Scheme.xlsx
+++ b/Grading Scheme/CS4800 Grading Scheme.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365.sharepoint.com/sites/stud-CS4800-SustainableICT/Gedeelde documenten/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C8BED7-D679-487C-B4A9-A126B85DA036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EBEFB3C-A2C6-477F-B14B-E16057359B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{1172C34F-1F46-43B9-92EF-666DBCB28265}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{1172C34F-1F46-43B9-92EF-666DBCB28265}"/>
   </bookViews>
   <sheets>
     <sheet name="AI" sheetId="1" r:id="rId1"/>
     <sheet name="Software" sheetId="2" r:id="rId2"/>
+    <sheet name="Presentation" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="66">
   <si>
     <t>Section/Grade</t>
   </si>
@@ -270,12 +293,127 @@
     <t>• JIT performance impacts are presented and explained in a clear and complete way, e.g. with references from documentation
 • code changes related to JIT implementation that improve performance result from either abstract reasoning or deep understanding of the experiment or both, e.g. implementing changes that address stress hotspots</t>
   </si>
+  <si>
+    <t>Learning objective/Grade</t>
+  </si>
+  <si>
+    <t>Potential Questions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LO3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Students </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>apply techniques that minimize system climate impacts.</t>
+    </r>
+  </si>
+  <si>
+    <t>• impact of Part 1 design decisions on environment is not explained, or system is designed without taking into account environmental impacts</t>
+  </si>
+  <si>
+    <t>• connection between design decisions made in Part 1 and environmental impacts revealed in Part 2 explained in a vague or hard-to-follow manner, e.g. general statements that could apply to other systems</t>
+  </si>
+  <si>
+    <t>• connection between design decisions and environmental impacts explained in a clear way, with minor gaps in detail or organization</t>
+  </si>
+  <si>
+    <t>• connection between design decisions and environmental impacts explained in a clear and complete way, e.g. effect on sustainability flows down directly from system properties
+• system is designed in a manner that reduces environmental impact, or, if not, students can explain why this happens</t>
+  </si>
+  <si>
+    <t>• To what extent the implementation of JIT reduce/increase your code's energy consumption? Why?
+• Would selecting a different AI model architecture have decreased your system's environmental impact?
+• What does your experiment highlight about the sustainability of the real-life workload?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LO4:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Students</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> analyze how each design technique affects system climate impacts.</t>
+    </r>
+  </si>
+  <si>
+    <t>• environmental impacts assessed in Part 2 are not presented</t>
+  </si>
+  <si>
+    <t>• results of environmental impact assessment presented in a vague or hard-to-follow manner, e.g. unclear whether emissions figures are CO2 or CO2-eq</t>
+  </si>
+  <si>
+    <t>• results of environmental impact assessment presented in a clear way, with minor gaps in detail or organization
+• recommendations for improvement given, with unclear applicability, e.g. change model architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• aspects of the designed system that concentrate the most environmental impact are specially distinguished
+• clear, complete, and directly applicable recommendations for improvement given
+</t>
+  </si>
+  <si>
+    <t>• How much energy does your selected model architecture or training/inference method save compared to standard? Why?
+• Where are the energy hotspots in your workload? Do you think this also happens in real life? How would you address these hotspots?
+• Does your design minimize both the carbon footprint and the water footprint, or did you have to make a trade-off? Which did you pick and why?</t>
+  </si>
+  <si>
+    <t>Note: all criteria require a passing grade to obtain a passing grade for the assignment. All sub-criteria need to be met to obtain the maximum grade.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +471,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -453,9 +599,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -539,6 +697,10 @@
     <xf numFmtId="10" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -546,6 +708,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="35"/>
     </xf>
@@ -892,238 +1055,238 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="44.42578125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="24"/>
-    <col min="8" max="8" width="44.42578125" style="24" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="24"/>
+    <col min="1" max="1" width="32.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="44.42578125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="28"/>
+    <col min="8" max="8" width="44.42578125" style="28" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="26">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="30">
         <f>SUM(F3:F4)</f>
         <v>0.35</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="31">
         <f>(F3*G3+F4*G4)/F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="17"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="138" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="33">
         <v>0.1</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8" ht="275.25" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="33">
         <v>0.25</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="26">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="30">
         <f>SUM(F6:F8)</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="31">
         <f>(F6*G6+F7*G7+F8*G8)/F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:8" ht="88.15" customHeight="1">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="33">
         <v>0.05</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" ht="100.9">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="33">
         <v>0.45</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:8" ht="104.45" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="33">
         <v>0.05</v>
       </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="26">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="30">
         <f>SUM(F10)</f>
         <v>0.1</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="31">
         <f>F10*G10/F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="17"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:8" ht="76.150000000000006" customHeight="1">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="31">
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="35">
         <v>0.1</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="17"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="38">
         <f>SUM(F2, F5, F9)</f>
         <v>1</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="37">
         <f>F2*G2+F5*G5+F9*G9</f>
         <v>0</v>
       </c>
-      <c r="H11" s="17"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="13" spans="1:8" ht="15.6">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="42" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1149,217 +1312,217 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="9">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="13">
         <f>SUM(F3:F4)</f>
         <v>0.5</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="14">
         <f>(F3*G3+F4*G4)/F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="17"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="222" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="15">
         <v>0.35</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="17"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8" ht="207.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="15">
         <v>0.15</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="17"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="9">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="13">
         <f>SUM(F6:F8)</f>
         <v>0.39999999999999997</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="14">
         <f>(F6*G6+F7*G7+F8*G8)/F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:8" ht="72">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="15">
         <v>0.05</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="17"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" ht="100.9">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="15">
         <v>0.3</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:8" ht="100.9">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="15">
         <v>0.05</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="17"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="9">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="13">
         <f>SUM(F10)</f>
         <v>0.1</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="14">
         <f>F10*G10/F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="17"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:8" ht="72">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="13">
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="17">
         <v>0.1</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="19">
         <f>SUM(F2, F5, F9)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="20">
         <f>F2*G2+F5*G5+F9*G9</f>
         <v>0</v>
       </c>
-      <c r="H11" s="17"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="H12" s="17"/>
+      <c r="H12" s="21"/>
     </row>
     <row r="13" spans="1:8" ht="15.6">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="42" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1367,6 +1530,120 @@
   <mergeCells count="1">
     <mergeCell ref="C10:E10"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051E3901-2D00-4B7A-AF1E-750AA7A841D8}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="65" customWidth="1"/>
+    <col min="9" max="9" width="41.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="158.44999999999999" customHeight="1">
+      <c r="A2" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="16"/>
+      <c r="H2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:9" ht="117" customHeight="1">
+      <c r="A3" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="E4" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="38">
+        <f>SUM(F2:F3)</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="37" cm="1">
+        <f t="array" aca="1" ref="G4" ca="1">SUM(F2:F6*G2:G6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.6">
+      <c r="B6" s="42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
